--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.51172</v>
+        <v>16.73073</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6235</v>
+        <v>16.35591</v>
       </c>
       <c r="E2" t="n">
-        <v>16.50691</v>
+        <v>16.46137</v>
       </c>
       <c r="F2" t="n">
-        <v>42.54054</v>
+        <v>42.60332</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05034</v>
+        <v>0.05032</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80578</v>
+        <v>1.83598</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.76204</v>
+        <v>16.84409</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29527</v>
+        <v>16.19287</v>
       </c>
       <c r="E3" t="n">
-        <v>16.49258</v>
+        <v>16.73239</v>
       </c>
       <c r="F3" t="n">
-        <v>42.34223</v>
+        <v>42.30477</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0505</v>
+        <v>0.04983</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84134</v>
+        <v>1.81221</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.71945</v>
+        <v>17.23019</v>
       </c>
       <c r="D4" t="n">
-        <v>16.43565</v>
+        <v>16.19078</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63918</v>
+        <v>16.30859</v>
       </c>
       <c r="F4" t="n">
-        <v>41.97234</v>
+        <v>41.85976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05119</v>
+        <v>0.05037</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8116</v>
+        <v>1.80611</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.79471</v>
+        <v>16.75364</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06239</v>
+        <v>15.7257</v>
       </c>
       <c r="E6" t="n">
-        <v>16.05472</v>
+        <v>16.09182</v>
       </c>
       <c r="F6" t="n">
-        <v>21.59023</v>
+        <v>21.35269</v>
       </c>
       <c r="G6" t="n">
-        <v>34.01318</v>
+        <v>34.26741</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81263</v>
+        <v>16.1442</v>
       </c>
       <c r="D7" t="n">
-        <v>15.7413</v>
+        <v>15.92198</v>
       </c>
       <c r="E7" t="n">
-        <v>16.74552</v>
+        <v>16.02758</v>
       </c>
       <c r="F7" t="n">
-        <v>21.1697</v>
+        <v>21.56912</v>
       </c>
       <c r="G7" t="n">
-        <v>33.84093</v>
+        <v>34.2914</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.71639</v>
+        <v>16.93567</v>
       </c>
       <c r="D8" t="n">
-        <v>16.00047</v>
+        <v>15.88691</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51907</v>
+        <v>16.04989</v>
       </c>
       <c r="F8" t="n">
-        <v>21.41125</v>
+        <v>21.22468</v>
       </c>
       <c r="G8" t="n">
-        <v>34.4142</v>
+        <v>34.69374</v>
       </c>
     </row>
   </sheetData>
